--- a/Uploads/Data/SampleEventWQ_TEMPLATE.xlsx
+++ b/Uploads/Data/SampleEventWQ_TEMPLATE.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Erica.Williams\Documents\GitHub\SQL-Database-Corrections\Uploads\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Erica.Levine\Documents\GitHub\SQL-Database-Corrections\Uploads\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BF83D92-C022-4246-996A-B976F3B42318}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98EE89B7-557F-41C5-BA28-E6CE7D87797E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2108D022-863A-4DDA-9361-349A7F55884E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{2108D022-863A-4DDA-9361-349A7F55884E}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="2" r:id="rId1"/>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11523" uniqueCount="2249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11547" uniqueCount="2254">
   <si>
     <t>SampleEventWQID</t>
   </si>
@@ -6807,6 +6807,21 @@
   </si>
   <si>
     <t>pH not recorded</t>
+  </si>
+  <si>
+    <t>TB Braden South</t>
+  </si>
+  <si>
+    <t>Proofed</t>
+  </si>
+  <si>
+    <t>Sex ratio project station</t>
+  </si>
+  <si>
+    <t>Added via SMSS for sex ratio project samples</t>
+  </si>
+  <si>
+    <t>TB Braden South 9</t>
   </si>
 </sst>
 </file>
@@ -6942,7 +6957,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -6970,6 +6985,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -8827,7 +8845,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9135BC8C-C095-4174-876F-A976B8C1179A}">
-  <dimension ref="A1:S815"/>
+  <dimension ref="A1:AF816"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.140625" style="2" bestFit="1" customWidth="1"/>
@@ -56052,7 +56070,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="801" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="801" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A801" s="2" t="s">
         <v>1753</v>
       </c>
@@ -56111,7 +56129,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="802" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="802" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A802" s="2" t="s">
         <v>1756</v>
       </c>
@@ -56170,7 +56188,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="803" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="803" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A803" s="2" t="s">
         <v>1759</v>
       </c>
@@ -56229,7 +56247,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="804" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="804" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A804" s="2" t="s">
         <v>1762</v>
       </c>
@@ -56288,7 +56306,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="805" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="805" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A805" s="2" t="s">
         <v>1765</v>
       </c>
@@ -56347,7 +56365,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="806" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="806" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A806" s="2" t="s">
         <v>1768</v>
       </c>
@@ -56406,7 +56424,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="807" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="807" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A807" s="2" t="s">
         <v>1771</v>
       </c>
@@ -56465,7 +56483,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="808" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="808" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A808" s="2" t="s">
         <v>1774</v>
       </c>
@@ -56524,7 +56542,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="809" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="809" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A809" s="2" t="s">
         <v>1777</v>
       </c>
@@ -56583,7 +56601,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="810" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="810" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A810" s="2" t="s">
         <v>1780</v>
       </c>
@@ -56642,7 +56660,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="811" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="811" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A811" s="2" t="s">
         <v>1783</v>
       </c>
@@ -56701,7 +56719,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="812" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="812" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A812" s="2" t="s">
         <v>1786</v>
       </c>
@@ -56760,7 +56778,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="813" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="813" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A813" s="2" t="s">
         <v>1789</v>
       </c>
@@ -56819,7 +56837,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="814" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="814" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A814" s="2" t="s">
         <v>1792</v>
       </c>
@@ -56878,7 +56896,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="815" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="815" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A815" s="2" t="s">
         <v>1795</v>
       </c>
@@ -56935,6 +56953,104 @@
       </c>
       <c r="S815" s="2" t="s">
         <v>78</v>
+      </c>
+    </row>
+    <row r="816" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A816" s="2">
+        <v>401</v>
+      </c>
+      <c r="B816" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C816" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="D816" s="2" t="s">
+        <v>2249</v>
+      </c>
+      <c r="E816" s="2">
+        <v>9</v>
+      </c>
+      <c r="F816" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G816" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H816" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I816" s="2">
+        <v>27.495699999999999</v>
+      </c>
+      <c r="J816" s="2">
+        <v>82.523679999999999</v>
+      </c>
+      <c r="K816" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="L816" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="M816" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="N816" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="O816" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="P816" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q816" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="R816" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="S816" s="3">
+        <v>46113</v>
+      </c>
+      <c r="T816" s="3">
+        <v>73050</v>
+      </c>
+      <c r="U816" s="2" t="s">
+        <v>2250</v>
+      </c>
+      <c r="V816" s="17">
+        <v>46141</v>
+      </c>
+      <c r="W816" s="2" t="s">
+        <v>1804</v>
+      </c>
+      <c r="X816" s="17">
+        <v>46141</v>
+      </c>
+      <c r="Y816" s="2" t="s">
+        <v>1804</v>
+      </c>
+      <c r="Z816" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="AA816" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="AB816" s="2" t="s">
+        <v>2251</v>
+      </c>
+      <c r="AC816" s="2" t="s">
+        <v>2252</v>
+      </c>
+      <c r="AD816" s="2" t="s">
+        <v>2253</v>
+      </c>
+      <c r="AE816" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="AF816" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
